--- a/Action/Data/CSV/MobEnemy/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy/MobEnemyData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\MobEnemy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00208969-8FCE-4C53-AE1C-89D7A7D7C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FD0614F-6722-4576-AE10-460C9544C58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MobEnemyData" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -684,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -724,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -830,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -972,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -980,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
@@ -994,7 +991,7 @@
         <v>20</v>
       </c>
       <c r="C1">
-        <v>-620</v>
+        <v>-800</v>
       </c>
       <c r="D1">
         <v>0</v>
@@ -1015,16 +1012,16 @@
         <v>1</v>
       </c>
       <c r="J1">
-        <f>G1*5</f>
-        <v>5</v>
+        <f>G1*20</f>
+        <v>20</v>
       </c>
       <c r="K1">
-        <f t="shared" ref="K1:L1" si="0">H1*5</f>
-        <v>5</v>
+        <f t="shared" ref="K1:L1" si="0">H1*20</f>
+        <v>20</v>
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -1032,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>-940</v>
+        <v>-1150</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1056,27 +1053,27 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J20" si="1">G2*5</f>
-        <v>5</v>
+        <f t="shared" ref="J2:J20" si="1">G2*20</f>
+        <v>20</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K20" si="2">H2*5</f>
-        <v>5</v>
+        <f t="shared" ref="K2:K20" si="2">H2*20</f>
+        <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L20" si="3">I2*5</f>
-        <v>5</v>
+        <f t="shared" ref="L2:L20" si="3">I2*20</f>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>-1150</v>
+        <v>-2000</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1098,26 +1095,26 @@
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C4">
-        <v>-1460</v>
+        <v>-2000</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1139,26 +1136,26 @@
       </c>
       <c r="J4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>-1280</v>
+        <v>-2260</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1180,26 +1177,26 @@
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>-1370</v>
+        <v>-2260</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1221,26 +1218,26 @@
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="B7">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>-1470</v>
+        <v>-2560</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1262,26 +1259,26 @@
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="B8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>-1590</v>
+        <v>-2560</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1303,15 +1300,15 @@
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -1319,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>-1680</v>
+        <v>-2560</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1344,15 +1341,15 @@
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -1360,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="C10">
-        <v>-1900</v>
+        <v>-3030</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1385,32 +1382,32 @@
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C11">
-        <v>-2360</v>
+        <v>-3080</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1426,32 +1423,32 @@
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K11">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="B12">
         <v>300</v>
       </c>
       <c r="C12">
-        <v>-2920</v>
+        <v>-2980</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1467,15 +1464,15 @@
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -1492,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1508,32 +1505,32 @@
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K13">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>730</v>
+        <v>990</v>
       </c>
       <c r="B14">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="C14">
-        <v>-3030</v>
+        <v>-3100</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1549,32 +1546,32 @@
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>1090</v>
+        <v>990</v>
       </c>
       <c r="B15">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="C15">
-        <v>-3030</v>
+        <v>-2960</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1590,20 +1587,20 @@
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>950</v>
+        <v>1555</v>
       </c>
       <c r="B16">
         <v>320</v>
@@ -1615,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1631,32 +1628,32 @@
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K16">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>990</v>
+        <v>3480</v>
       </c>
       <c r="B17">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C17">
-        <v>-3030</v>
+        <v>-3230</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1672,32 +1669,32 @@
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K17">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L17">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>1230</v>
+        <v>3480</v>
       </c>
       <c r="B18">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C18">
-        <v>-3030</v>
+        <v>-3430</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1713,32 +1710,32 @@
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K18">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L18">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>1030</v>
+        <v>3480</v>
       </c>
       <c r="B19">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C19">
-        <v>-3030</v>
+        <v>-2830</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1754,32 +1751,32 @@
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L19">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>1050</v>
+        <v>3480</v>
       </c>
       <c r="B20">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C20">
-        <v>-3030</v>
+        <v>-2630</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1795,15 +1792,220 @@
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K20">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L20">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>3480</v>
+      </c>
+      <c r="B21">
+        <v>360</v>
+      </c>
+      <c r="C21">
+        <v>-3030</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>4.71</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <f t="shared" ref="J21:J25" si="4">G21*20</f>
+        <v>20</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ref="K21:K25" si="5">H21*20</f>
+        <v>20</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ref="L21:L25" si="6">I21*20</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>3680</v>
+      </c>
+      <c r="B22">
+        <v>360</v>
+      </c>
+      <c r="C22">
+        <v>-3130</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>4.71</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>3680</v>
+      </c>
+      <c r="B23">
+        <v>360</v>
+      </c>
+      <c r="C23">
+        <v>-2930</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>4.71</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>3280</v>
+      </c>
+      <c r="B24">
+        <v>360</v>
+      </c>
+      <c r="C24">
+        <v>-3130</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>4.71</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>3280</v>
+      </c>
+      <c r="B25">
+        <v>360</v>
+      </c>
+      <c r="C25">
+        <v>-2930</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>4.71</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Action/Data/CSV/MobEnemy/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy/MobEnemyData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\MobEnemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FD0614F-6722-4576-AE10-460C9544C58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE8DC6B-2215-4E0F-8D94-F334AD5C9C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MobEnemyData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1053,15 +1053,15 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J20" si="1">G2*20</f>
+        <f t="shared" ref="J2:J24" si="1">G2*20</f>
         <v>20</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K20" si="2">H2*20</f>
+        <f t="shared" ref="K2:K25" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L20" si="3">I2*20</f>
+        <f t="shared" ref="L2:L25" si="3">I2*20</f>
         <v>20</v>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" ref="J21:J25" si="4">G21*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K21">
-        <f t="shared" ref="K21:K25" si="5">H21*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" ref="L21:L25" si="6">I21*20</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
@@ -1873,15 +1873,15 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
@@ -1914,15 +1914,15 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
@@ -1955,15 +1955,15 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
@@ -1996,15 +1996,15 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <f t="shared" si="4"/>
+        <f>G25*20</f>
         <v>20</v>
       </c>
       <c r="K25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
